--- a/Rstudio/Static chambers/Data/chamber_data.xlsx
+++ b/Rstudio/Static chambers/Data/chamber_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lorenzobenedetti/Desktop/Università/DiANA/Dottorato/Danimarca/AU/Agroscena Next/DFC_SC_Lorenzo_Pablo/Static chambers/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73120BF-93D1-6D42-8BEB-4CB6E36DB3A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D198AD-B632-E74F-8A88-3C7C4E01E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="68800" windowHeight="28200" xr2:uid="{E1C4C9E1-F7C4-554E-99BF-1BC5AECA9C44}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{E1C4C9E1-F7C4-554E-99BF-1BC5AECA9C44}"/>
   </bookViews>
   <sheets>
     <sheet name="N2O" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="27">
   <si>
     <t>Chamber</t>
   </si>
@@ -5110,7 +5110,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9BA086E-BC2B-DC49-993C-D93BAB2A8E90}" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B9BA086E-BC2B-DC49-993C-D93BAB2A8E90}" name="Tabella pivot2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:K11" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -6443,7 +6443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4EBCB2-91B0-2349-B1D4-DE0EC39EEC3A}">
-  <dimension ref="A1:J531"/>
+  <dimension ref="A1:J559"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="10.83203125" style="14"/>
@@ -20547,7 +20547,7 @@
         <v>9</v>
       </c>
       <c r="C504" s="13">
-        <v>0.43072916666666666</v>
+        <v>0.43177083333333333</v>
       </c>
       <c r="D504" s="13">
         <v>0.43281249999999999</v>
@@ -21321,6 +21321,790 @@
       </c>
       <c r="J531" s="3">
         <v>530</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A532" s="3">
+        <v>12</v>
+      </c>
+      <c r="B532" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C532" s="13">
+        <v>0.41562500000000002</v>
+      </c>
+      <c r="D532" s="13">
+        <v>0.41770833333333335</v>
+      </c>
+      <c r="E532" s="3">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="F532" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G532" s="3"/>
+      <c r="H532" s="3"/>
+      <c r="I532" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J532" s="3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A533" s="3">
+        <v>5</v>
+      </c>
+      <c r="B533" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C533" s="13">
+        <v>0.41822916666666665</v>
+      </c>
+      <c r="D533" s="13">
+        <v>0.42031249999999998</v>
+      </c>
+      <c r="E533" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="F533" s="3">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="G533" s="3"/>
+      <c r="H533" s="3"/>
+      <c r="I533" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J533" s="3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A534" s="3">
+        <v>21</v>
+      </c>
+      <c r="B534" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C534" s="13">
+        <v>0.42083333333333334</v>
+      </c>
+      <c r="D534" s="13">
+        <v>0.42291666666666666</v>
+      </c>
+      <c r="E534" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="F534" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="G534" s="3"/>
+      <c r="H534" s="3"/>
+      <c r="I534" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J534" s="3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A535" s="3">
+        <v>3</v>
+      </c>
+      <c r="B535" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C535" s="13">
+        <v>0.42343750000000002</v>
+      </c>
+      <c r="D535" s="13">
+        <v>0.42552083333333335</v>
+      </c>
+      <c r="E535" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F535" s="3">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="G535" s="3"/>
+      <c r="H535" s="3"/>
+      <c r="I535" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J535" s="3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A536" s="3">
+        <v>27</v>
+      </c>
+      <c r="B536" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C536" s="13">
+        <v>0.42656250000000001</v>
+      </c>
+      <c r="D536" s="13">
+        <v>0.42864583333333334</v>
+      </c>
+      <c r="E536" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F536" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="G536" s="3"/>
+      <c r="H536" s="3"/>
+      <c r="I536" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J536" s="3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A537" s="3">
+        <v>9</v>
+      </c>
+      <c r="B537" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C537" s="13">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="D537" s="13">
+        <v>0.43125000000000002</v>
+      </c>
+      <c r="E537" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F537" s="3">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="G537" s="3"/>
+      <c r="H537" s="3"/>
+      <c r="I537" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J537" s="3">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A538" s="3">
+        <v>16</v>
+      </c>
+      <c r="B538" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C538" s="13">
+        <v>0.43177083333333333</v>
+      </c>
+      <c r="D538" s="13">
+        <v>0.43385416666666665</v>
+      </c>
+      <c r="E538" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F538" s="3">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G538" s="3"/>
+      <c r="H538" s="3"/>
+      <c r="I538" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J538" s="3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A539" s="3">
+        <v>1</v>
+      </c>
+      <c r="B539" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C539" s="13">
+        <v>0.43437500000000001</v>
+      </c>
+      <c r="D539" s="13">
+        <v>0.43645833333333334</v>
+      </c>
+      <c r="E539" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F539" s="3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="G539" s="3"/>
+      <c r="H539" s="3"/>
+      <c r="I539" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J539" s="3">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A540" s="3">
+        <v>24</v>
+      </c>
+      <c r="B540" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C540" s="13">
+        <v>0.4375</v>
+      </c>
+      <c r="D540" s="13">
+        <v>0.43958333333333333</v>
+      </c>
+      <c r="E540" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F540" s="3">
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="G540" s="3"/>
+      <c r="H540" s="3"/>
+      <c r="I540" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J540" s="3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A541" s="3">
+        <v>7</v>
+      </c>
+      <c r="B541" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C541" s="13">
+        <v>0.44062499999999999</v>
+      </c>
+      <c r="D541" s="13">
+        <v>0.44270833333333331</v>
+      </c>
+      <c r="E541" s="3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="F541" s="3">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="G541" s="3"/>
+      <c r="H541" s="3"/>
+      <c r="I541" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J541" s="3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A542" s="3">
+        <v>18</v>
+      </c>
+      <c r="B542" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C542" s="13">
+        <v>0.44322916666666667</v>
+      </c>
+      <c r="D542" s="13">
+        <v>0.4453125</v>
+      </c>
+      <c r="E542" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F542" s="3">
+        <v>0.39800000000000002</v>
+      </c>
+      <c r="G542" s="3"/>
+      <c r="H542" s="3"/>
+      <c r="I542" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J542" s="3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A543" s="3">
+        <v>14</v>
+      </c>
+      <c r="B543" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C543" s="13">
+        <v>0.44635416666666666</v>
+      </c>
+      <c r="D543" s="13">
+        <v>0.44843749999999999</v>
+      </c>
+      <c r="E543" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F543" s="3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="G543" s="3"/>
+      <c r="H543" s="3"/>
+      <c r="I543" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J543" s="3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A544" s="3">
+        <v>2</v>
+      </c>
+      <c r="B544" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C544" s="13">
+        <v>0.44947916666666665</v>
+      </c>
+      <c r="D544" s="13">
+        <v>0.45156249999999998</v>
+      </c>
+      <c r="E544" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F544" s="3">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="G544" s="3"/>
+      <c r="H544" s="3"/>
+      <c r="I544" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J544" s="3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A545" s="3">
+        <v>26</v>
+      </c>
+      <c r="B545" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C545" s="13">
+        <v>0.45260416666666664</v>
+      </c>
+      <c r="D545" s="13">
+        <v>0.45468750000000002</v>
+      </c>
+      <c r="E545" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F545" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="G545" s="3"/>
+      <c r="H545" s="3"/>
+      <c r="I545" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J545" s="3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A546" s="3">
+        <v>11</v>
+      </c>
+      <c r="B546" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C546" s="13">
+        <v>0.45572916666666669</v>
+      </c>
+      <c r="D546" s="13">
+        <v>0.45781250000000001</v>
+      </c>
+      <c r="E546" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F546" s="3">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="G546" s="3"/>
+      <c r="H546" s="3"/>
+      <c r="I546" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J546" s="3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A547" s="3">
+        <v>20</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C547" s="13">
+        <v>0.45885416666666667</v>
+      </c>
+      <c r="D547" s="13">
+        <v>0.4609375</v>
+      </c>
+      <c r="E547" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="F547" s="3">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="G547" s="3"/>
+      <c r="H547" s="3"/>
+      <c r="I547" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J547" s="3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A548" s="3">
+        <v>4</v>
+      </c>
+      <c r="B548" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C548" s="13">
+        <v>0.46197916666666666</v>
+      </c>
+      <c r="D548" s="13">
+        <v>0.46406249999999999</v>
+      </c>
+      <c r="E548" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="F548" s="3">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="G548" s="3"/>
+      <c r="H548" s="3"/>
+      <c r="I548" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J548" s="3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A549" s="3">
+        <v>28</v>
+      </c>
+      <c r="B549" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C549" s="13">
+        <v>0.46510416666666665</v>
+      </c>
+      <c r="D549" s="13">
+        <v>0.46718749999999998</v>
+      </c>
+      <c r="E549" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="F549" s="3">
+        <v>0.40799999999999997</v>
+      </c>
+      <c r="G549" s="3"/>
+      <c r="H549" s="3"/>
+      <c r="I549" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J549" s="3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A550" s="3">
+        <v>8</v>
+      </c>
+      <c r="B550" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C550" s="13">
+        <v>0.46822916666666664</v>
+      </c>
+      <c r="D550" s="13">
+        <v>0.47031250000000002</v>
+      </c>
+      <c r="E550" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="F550" s="3">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="G550" s="3"/>
+      <c r="H550" s="3"/>
+      <c r="I550" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J550" s="3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A551" s="3">
+        <v>22</v>
+      </c>
+      <c r="B551" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C551" s="13">
+        <v>0.47135416666666669</v>
+      </c>
+      <c r="D551" s="13">
+        <v>0.47343750000000001</v>
+      </c>
+      <c r="E551" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="F551" s="3">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G551" s="3"/>
+      <c r="H551" s="3"/>
+      <c r="I551" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J551" s="3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A552" s="3">
+        <v>6</v>
+      </c>
+      <c r="B552" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C552" s="13">
+        <v>0.47447916666666667</v>
+      </c>
+      <c r="D552" s="13">
+        <v>0.4765625</v>
+      </c>
+      <c r="E552" s="3">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="F552" s="3">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="G552" s="3"/>
+      <c r="H552" s="3"/>
+      <c r="I552" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J552" s="3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A553" s="3">
+        <v>19</v>
+      </c>
+      <c r="B553" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C553" s="13">
+        <v>0.47760416666666666</v>
+      </c>
+      <c r="D553" s="13">
+        <v>0.47968749999999999</v>
+      </c>
+      <c r="E553" s="3">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="F553" s="3">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="G553" s="3"/>
+      <c r="H553" s="3"/>
+      <c r="I553" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J553" s="3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A554" s="3">
+        <v>10</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C554" s="13">
+        <v>0.48020833333333335</v>
+      </c>
+      <c r="D554" s="13">
+        <v>0.48229166666666667</v>
+      </c>
+      <c r="E554" s="3">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="F554" s="3">
+        <v>0.38800000000000001</v>
+      </c>
+      <c r="G554" s="3"/>
+      <c r="H554" s="3"/>
+      <c r="I554" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J554" s="3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A555" s="3">
+        <v>13</v>
+      </c>
+      <c r="B555" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C555" s="13">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="D555" s="13">
+        <v>0.48541666666666666</v>
+      </c>
+      <c r="E555" s="3">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="F555" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="G555" s="3"/>
+      <c r="H555" s="3"/>
+      <c r="I555" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J555" s="3">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A556" s="3">
+        <v>23</v>
+      </c>
+      <c r="B556" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C556" s="13">
+        <v>0.48645833333333333</v>
+      </c>
+      <c r="D556" s="13">
+        <v>0.48854166666666665</v>
+      </c>
+      <c r="E556" s="3">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="F556" s="3">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="G556" s="3"/>
+      <c r="H556" s="3"/>
+      <c r="I556" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J556" s="3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A557" s="3">
+        <v>25</v>
+      </c>
+      <c r="B557" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C557" s="13">
+        <v>0.48923611111111109</v>
+      </c>
+      <c r="D557" s="13">
+        <v>0.49114583333333334</v>
+      </c>
+      <c r="E557" s="3">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="F557" s="3">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="G557" s="3"/>
+      <c r="H557" s="3"/>
+      <c r="I557" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J557" s="3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A558" s="3">
+        <v>15</v>
+      </c>
+      <c r="B558" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C558" s="13">
+        <v>0.4921875</v>
+      </c>
+      <c r="D558" s="13">
+        <v>0.49427083333333333</v>
+      </c>
+      <c r="E558" s="3">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="F558" s="3">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="G558" s="3"/>
+      <c r="H558" s="3"/>
+      <c r="I558" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J558" s="3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A559" s="3">
+        <v>17</v>
+      </c>
+      <c r="B559" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C559" s="13">
+        <v>0.49531249999999999</v>
+      </c>
+      <c r="D559" s="13">
+        <v>0.49739583333333331</v>
+      </c>
+      <c r="E559" s="3">
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="F559" s="3">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="G559" s="3"/>
+      <c r="H559" s="3"/>
+      <c r="I559" s="5">
+        <v>46031</v>
+      </c>
+      <c r="J559" s="3">
+        <v>558</v>
       </c>
     </row>
   </sheetData>
